--- a/esyluban/examples/dev/DataTables/test/#TestFormat.xlsx
+++ b/esyluban/examples/dev/DataTables/test/#TestFormat.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestFormat" &amp; value_type="test.TestFormat" &amp; mode="map" &amp; read_schema_from_file="true" &amp; input="test/#TestFormat.xlsx" &amp; output="test_tbtestformat"</t>
+          <t>full_name="test.TbTestFormat" &amp; read_schema_from_file="true" &amp; input="test/#TestFormat.xlsx"</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>

--- a/esyluban/examples/dev/DataTables/test/#TestFormat.xlsx
+++ b/esyluban/examples/dev/DataTables/test/#TestFormat.xlsx
@@ -894,9 +894,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AF1:AH1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AI1:AK1"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AF2:AH2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
